--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/updateAdminSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/updateAdminSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="145">
-  <si>
-    <t>Statement: updateAdminSchema – validate partial update for an admin. All optional.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="189">
+  <si>
+    <t>Statement: updateAdminSchema – Validates a partial update for an admin using Zod safeParse. All fields are optional; an empty object is valid. Returns { success: true, data } when every supplied field satisfies its constraint. Returns { success: false, error } with a path pointing to the offending field when any supplied field violates its constraint. Field constraints when present: email (valid email format; surrounding whitespace trimmed), fullName (8–64 characters after trimming, not whitespace-only; surrounding whitespace trimmed), phone (E.164 format: +[1-9]\d{1,14}; surrounding whitespace trimmed), dateOfBirth (YYYY-MM-DD, strictly before today), password (8–64 characters with at least one uppercase letter, one digit, and one special character). Note: updateAdminSchema has no membershipStart field.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: Partial&lt;{ email, fullName, phone, dateOfBirth, password }&gt;</t>
+    <t>Input: Partial&lt;{ email: string, fullName: string, phone: string, dateOfBirth: string, password: string }&gt;</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Same constraints apply when present.</t>
+    <t>Input is passed directly to updateAdminSchema.safeParse(). All fields are optional. When a field is present it is subject to the same constraints as in createAdminSchema. fullName: 8–64 characters after trim, not whitespace-only. password: 8–64 characters, at least one uppercase letter, one digit, one special character. dateOfBirth: YYYY-MM-DD, strictly before today.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: UpdateAdminInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data contains only the supplied (trimmed) fields. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,52 +64,82 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Empty object</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Valid RFC</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>FullName</t>
-  </si>
-  <si>
-    <t>8-64 chars</t>
-  </si>
-  <si>
-    <t>Invalid length</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Valid E.164</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Has complexity</t>
-  </si>
-  <si>
-    <t>Missing complexity</t>
-  </si>
-  <si>
-    <t>DateOfBirth</t>
-  </si>
-  <si>
-    <t>Past date</t>
-  </si>
-  <si>
-    <t>Future date</t>
+    <t>Empty input</t>
+  </si>
+  <si>
+    <t>Empty object {} → success: true, parsed data is {}</t>
+  </si>
+  <si>
+    <t>email value</t>
+  </si>
+  <si>
+    <t>email: "admin-new@example.com" → success: true, parsed email matches input</t>
+  </si>
+  <si>
+    <t>email: "not-valid" (missing @) → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>fullName value</t>
+  </si>
+  <si>
+    <t>fullName: "Updated Admin Test" (valid length) → success: true, parsed fullName matches input</t>
+  </si>
+  <si>
+    <t>phone value</t>
+  </si>
+  <si>
+    <t>phone: "+40712345678" (valid E.164) → success: true, parsed phone matches input</t>
+  </si>
+  <si>
+    <t>phone: "invalid-phone" (no country code prefix) → success: false, error path contains "phone"</t>
+  </si>
+  <si>
+    <t>password uppercase</t>
+  </si>
+  <si>
+    <t>password: "secure1@pass" (no uppercase letter) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password digit</t>
+  </si>
+  <si>
+    <t>password: "SecureP@ss" (no digit) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password special char</t>
+  </si>
+  <si>
+    <t>password: "NewP@ss1" (meets all rules) → success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>password: "SecurePass1" (no special character) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>dateOfBirth value</t>
+  </si>
+  <si>
+    <t>dateOfBirth: yesterday (YYYY-MM-DD, strictly before today) → success: true, parsed dateOfBirth matches input</t>
+  </si>
+  <si>
+    <t>fullName content</t>
+  </si>
+  <si>
+    <t>fullName: "  Updated Admin Test  " (surrounding whitespace) → success: true, parsed fullName is "Updated Admin Test"</t>
+  </si>
+  <si>
+    <t>fullName: "         " (whitespace-only) → success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>email whitespace</t>
+  </si>
+  <si>
+    <t>email: "  admin-new@example.com  " (surrounding whitespace) → success: true, parsed email is "admin-new@example.com"</t>
+  </si>
+  <si>
+    <t>phone whitespace</t>
+  </si>
+  <si>
+    <t>phone: "  +40712345678  " (surrounding whitespace) → success: true, parsed phone is "+40712345678"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -130,7 +160,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>success: true</t>
+    <t>empty object {}</t>
+  </si>
+  <si>
+    <t>success: true, parsed data is {}</t>
   </si>
   <si>
     <t>Passed</t>
@@ -139,49 +172,100 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>{email: "admin-new@example.com"}</t>
+    <t>object with only email: "admin-new@example.com"</t>
+  </si>
+  <si>
+    <t>success: true, parsed email is "admin-new@example.com"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>{fullName: "Updated Admin Test"}</t>
+    <t>object with only fullName: "Updated Admin Test"</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "Updated Admin Test"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>{phone: "+40712345678"}</t>
+    <t>object with only phone: "+40712345678"</t>
+  </si>
+  <si>
+    <t>success: true, parsed phone is "+40712345678"</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>object with only password: "NewP@ss1" (meets all rules)</t>
+  </si>
+  <si>
+    <t>success: true, parsed password is "NewP@ss1"</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>object with only dateOfBirth set to yesterday (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>success: true, parsed dateOfBirth is yesterday's date string</t>
+  </si>
+  <si>
+    <t>object with only email: "not-valid" (missing @)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>object with only phone: "invalid-phone" (no country code prefix)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "phone"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>{password: "NewP@ss1"}</t>
+    <t>object with only password: "secure1@pass" (no uppercase letter)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "password"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>{dateOfBirth: "yesterday"}</t>
-  </si>
-  <si>
-    <t>{email: "not-valid"}</t>
-  </si>
-  <si>
-    <t>success: false</t>
-  </si>
-  <si>
-    <t>{phone: "invalid-phone"}</t>
-  </si>
-  <si>
-    <t>{password: "secure1@pass"}</t>
-  </si>
-  <si>
-    <t>{password: "SecureP@ss"}</t>
-  </si>
-  <si>
-    <t>{password: "SecurePass1"}</t>
+    <t>object with only password: "SecureP@ss" (no digit)</t>
+  </si>
+  <si>
+    <t>object with only password: "SecurePass1" (no special character)</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>object with only fullName: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "fullName"</t>
+  </si>
+  <si>
+    <t>object with only fullName: "  Updated Admin Test  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>object with only email: "  admin-new@example.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>object with only phone: "  +40712345678  " (surrounding whitespace)</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -190,133 +274,208 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>FullName length</t>
-  </si>
-  <si>
-    <t>7 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>8 chars (At Min)</t>
-  </si>
-  <si>
-    <t>9 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>63 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>64 chars (At Max)</t>
-  </si>
-  <si>
-    <t>65 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>Password length</t>
-  </si>
-  <si>
-    <t>DateOfBirth boundary</t>
-  </si>
-  <si>
-    <t>Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>Today (Invalid)</t>
-  </si>
-  <si>
-    <t>Tomorrow (Invalid)</t>
+    <t>fullName length</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(7) (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(8) (min): at minimum → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(9) (min + 1): above minimum → success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(63) (max - 1): below maximum → success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(64) (max): at maximum → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: "A".repeat(65) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(4) (length 7, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(5) (length 8, min): at minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(6) (length 9, min + 1): above minimum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(60) (length 63, max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(61) (length 64, max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(62) (length 65, max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth boundary</t>
+  </si>
+  <si>
+    <t>dateOfBirth: yesterday (one day before today, YYYY-MM-DD): strictly before today → success: true</t>
+  </si>
+  <si>
+    <t>dateOfBirth: today (YYYY-MM-DD): not before today → success: false</t>
+  </si>
+  <si>
+    <t>dateOfBirth: tomorrow (one day after today, YYYY-MM-DD): future → success: false</t>
+  </si>
+  <si>
+    <t>fullName whitespace + trim</t>
+  </si>
+  <si>
+    <t>fullName: " ".repeat(8) (8 whitespace chars, empty after trim) → success: false</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(8) + " " (8 real chars after trim, at minimum) → success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(64) + " " (64 real chars after trim, at maximum) → success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>fullName: " " + "A".repeat(65) + " " (65 real chars after trim, above maximum) → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 FullName 7ch</t>
-  </si>
-  <si>
-    <t>fullName len 7</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 8ch</t>
-  </si>
-  <si>
-    <t>fullName len 8</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 9ch</t>
-  </si>
-  <si>
-    <t>fullName len 9</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 63ch</t>
-  </si>
-  <si>
-    <t>fullName len 63</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 64ch</t>
-  </si>
-  <si>
-    <t>fullName len 64</t>
-  </si>
-  <si>
-    <t>BVA-1 FullName 65ch</t>
-  </si>
-  <si>
-    <t>fullName len 65</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 7ch</t>
-  </si>
-  <si>
-    <t>password len 7</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 8ch</t>
-  </si>
-  <si>
-    <t>password len 8</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 9ch</t>
-  </si>
-  <si>
-    <t>password len 9</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 63ch</t>
-  </si>
-  <si>
-    <t>password len 63</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 64ch</t>
-  </si>
-  <si>
-    <t>password len 64</t>
-  </si>
-  <si>
-    <t>BVA-2 Password 65ch</t>
-  </si>
-  <si>
-    <t>password len 65</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Yesterday</t>
-  </si>
-  <si>
-    <t>dob Yesterday</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Today</t>
-  </si>
-  <si>
-    <t>dob Today</t>
-  </si>
-  <si>
-    <t>BVA-3 DOB Tomorrow</t>
-  </si>
-  <si>
-    <t>dob Tomorrow</t>
+    <t>BVA-1  (fullName=7)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(7) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (fullName=8)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(8) (8 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>BVA-3  (fullName=9)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(9) (9 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-4  (fullName=63)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(63) (63 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-5  (fullName=64)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(64) (64 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed fullName is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-6  (fullName=65)</t>
+  </si>
+  <si>
+    <t>object with only fullName: "A".repeat(65) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-7  (pwd=7)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(4) (7 characters, meets all rules except minimum length)</t>
+  </si>
+  <si>
+    <t>BVA-8  (pwd=8)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(5) (8 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>BVA-9  (pwd=9)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(6) (9 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-10 (pwd=63)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(60) (63 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-11 (pwd=64)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(61) (64 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-12 (pwd=65)</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(62) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-13 (dob=yest)</t>
+  </si>
+  <si>
+    <t>object with only dateOfBirth set to yesterday (one day before today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-14 (dob=today)</t>
+  </si>
+  <si>
+    <t>object with only dateOfBirth set to today (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "dateOfBirth"</t>
+  </si>
+  <si>
+    <t>BVA-15 (dob=tmrw)</t>
+  </si>
+  <si>
+    <t>object with only dateOfBirth set to tomorrow (one day after today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-16 (ws=8)</t>
+  </si>
+  <si>
+    <t>object with only fullName: " ".repeat(8) (8 whitespace characters, empty after trim)</t>
+  </si>
+  <si>
+    <t>BVA-17 (pad→8)</t>
+  </si>
+  <si>
+    <t>object with only fullName: " " + "A".repeat(8) + " " (8 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-18 (pad→64)</t>
+  </si>
+  <si>
+    <t>object with only fullName: " " + "A".repeat(64) + " " (64 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-19 (pad→65)</t>
+  </si>
+  <si>
+    <t>object with only fullName: " " + "A".repeat(65) + " " (65 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -325,91 +484,64 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Empty object {}</t>
-  </si>
-  <si>
-    <t>Valid email only</t>
-  </si>
-  <si>
-    <t>Valid fullName only</t>
-  </si>
-  <si>
-    <t>Valid phone only</t>
-  </si>
-  <si>
-    <t>Valid password only</t>
-  </si>
-  <si>
-    <t>Valid dob (Yesterday)</t>
-  </si>
-  <si>
-    <t>Email format invalid</t>
-  </si>
-  <si>
-    <t>Phone format invalid</t>
-  </si>
-  <si>
-    <t>Password no uppercase</t>
-  </si>
-  <si>
-    <t>Password no number</t>
-  </si>
-  <si>
-    <t>Password no special</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>fullName len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>fullName len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>fullName len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>fullName len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>fullName len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>password len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>password len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>password len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>password len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>password len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>password len 65 (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>dob Yesterday (Valid)</t>
-  </si>
-  <si>
-    <t>dob Today (At boundary - invalid)</t>
-  </si>
-  <si>
-    <t>dob Tomorrow (Future boundary)</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>object with only password: "P1@" + "a".repeat(4) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
   </si>
   <si>
     <t>Testing</t>
@@ -442,7 +574,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>SCHEMA-06</t>
   </si>
   <si>
     <t>n/a</t>
@@ -967,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1028,7 +1160,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1036,13 +1168,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1053,10 +1185,10 @@
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1064,13 +1196,83 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1080,420 +1282,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>3</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1507,19 +1295,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1527,16 +1315,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1544,16 +1332,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1561,16 +1349,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1578,16 +1366,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1595,16 +1383,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1612,16 +1400,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1629,16 +1417,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1646,16 +1434,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1663,16 +1451,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1680,16 +1468,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1697,16 +1485,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1714,16 +1502,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1731,16 +1519,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1748,16 +1536,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1765,16 +1553,610 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>98</v>
       </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1785,7 +2167,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1798,22 +2180,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1841,19 +2223,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1861,19 +2243,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1881,19 +2263,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1901,19 +2283,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1921,19 +2303,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1941,19 +2323,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1961,19 +2343,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1981,19 +2363,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2001,19 +2383,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2021,19 +2403,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,19 +2423,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,19 +2443,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,19 +2463,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,19 +2483,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,16 +2506,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,16 +2526,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2164,36 +2546,36 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,16 +2586,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,16 +2606,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2244,16 +2626,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,16 +2646,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2284,16 +2666,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2304,16 +2686,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2324,16 +2706,176 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2361,16 +2903,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2378,45 +2920,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="B3" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2425,19 +2967,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/updateAdminSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/updateAdminSchema-bbt-form.xlsx
@@ -574,7 +574,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-06</t>
+    <t>SCHEMA-08</t>
   </si>
   <si>
     <t>n/a</t>
